--- a/data/trans_bre/KIDM_C_3_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/KIDM_C_3_R-Estudios-trans_bre.xlsx
@@ -660,17 +660,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 6,59</t>
+          <t>-6,11; 6,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,42; 12,83</t>
+          <t>-9,72; 11,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-22,85; 3,25</t>
+          <t>-22,45; 2,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -685,12 +685,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-60,87; 281,49</t>
+          <t>-59,67; 207,97</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-90,28; 62,58</t>
+          <t>-100,0; 74,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 5,12</t>
+          <t>-1,71; 5,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,45; 10,91</t>
+          <t>0,15; 11,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 3,73</t>
+          <t>-4,99; 3,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 6,84</t>
+          <t>-0,68; 6,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-33,7; 193,48</t>
+          <t>-33,25; 199,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,0; 118,84</t>
+          <t>0,58; 122,74</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-41,78; 51,58</t>
+          <t>-42,5; 53,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-34,44; 696,08</t>
+          <t>-27,09; 615,22</t>
         </is>
       </c>
     </row>
@@ -860,37 +860,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 7,76</t>
+          <t>-5,55; 7,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,11; 6,73</t>
+          <t>-12,23; 6,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 9,71</t>
+          <t>-6,32; 10,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 0,0</t>
+          <t>-5,84; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 916,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-71,95; 108,98</t>
+          <t>-71,91; 102,43</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-53,02; 178,36</t>
+          <t>-53,19; 205,29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 4,05</t>
+          <t>-1,46; 4,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 7,88</t>
+          <t>-0,94; 8,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 2,94</t>
+          <t>-4,86; 2,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 5,1</t>
+          <t>-0,88; 4,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-25,9; 139,95</t>
+          <t>-28,08; 142,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 77,65</t>
+          <t>-7,3; 85,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-38,98; 36,91</t>
+          <t>-42,29; 34,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-36,27; 561,79</t>
+          <t>-38,01; 569,29</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/KIDM_C_3_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/KIDM_C_3_R-Estudios-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores de los que se han reido mucho o muchísimo otros menores (autopercepción menor)</t>
+          <t>Menores de los/as que se han reído mucho o muchísimo otros/as menores (autopercepción menor)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -660,17 +660,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 6,53</t>
+          <t>-6,6; 6,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,72; 11,59</t>
+          <t>-11,7; 11,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-22,45; 2,97</t>
+          <t>-21,77; 3,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -680,17 +680,17 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-59,67; 207,97</t>
+          <t>-67,93; 239,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 74,33</t>
+          <t>-90,33; 66,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 5,24</t>
+          <t>-1,5; 5,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 11,55</t>
+          <t>0,14; 11,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 3,84</t>
+          <t>-5,15; 3,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 6,86</t>
+          <t>-0,73; 6,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-33,25; 199,18</t>
+          <t>-29,35; 197,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 122,74</t>
+          <t>2,29; 124,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-42,5; 53,27</t>
+          <t>-44,72; 51,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-27,09; 615,22</t>
+          <t>-44,56; 632,74</t>
         </is>
       </c>
     </row>
@@ -860,37 +860,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 7,74</t>
+          <t>-5,65; 7,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,23; 6,96</t>
+          <t>-10,89; 7,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 10,0</t>
+          <t>-6,52; 10,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 0,0</t>
+          <t>-6,28; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-71,91; 102,43</t>
+          <t>-70,8; 132,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-53,19; 205,29</t>
+          <t>-56,26; 212,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 4,06</t>
+          <t>-1,51; 4,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 8,2</t>
+          <t>-0,73; 7,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 2,84</t>
+          <t>-4,68; 2,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 4,91</t>
+          <t>-0,71; 5,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-28,08; 142,54</t>
+          <t>-30,37; 149,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-7,3; 85,02</t>
+          <t>-5,5; 83,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-42,29; 34,79</t>
+          <t>-39,86; 34,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-38,01; 569,29</t>
+          <t>-31,76; 617,21</t>
         </is>
       </c>
     </row>
